--- a/diseases/d118/2026-2029.xlsx
+++ b/diseases/d118/2026-2029.xlsx
@@ -1998,6 +1998,151 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>spotted-fever-rickettsiosis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Spotted fever rickettsiosis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Spotted fever rickettsiosis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>斑点热立克次体病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2031,7 +2176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2259,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2124,7 +2269,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d118/2026-2029.xlsx
+++ b/diseases/d118/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4445,6 +4580,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4590,6 +4730,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4726,6 +4871,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4862,6 +5012,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4998,6 +5153,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5134,6 +5294,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5270,6 +5435,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5406,6 +5576,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5542,6 +5717,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5678,6 +5858,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5814,6 +5999,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5950,6 +6140,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6086,6 +6281,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6222,6 +6422,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6358,6 +6563,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6494,6 +6704,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6630,6 +6845,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6766,6 +6986,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6902,6 +7127,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7038,6 +7268,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7174,6 +7409,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7310,6 +7550,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7446,6 +7691,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7582,6 +7832,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7718,6 +7973,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7854,6 +8114,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7990,6 +8255,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8126,6 +8396,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8262,6 +8537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8407,6 +8687,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8543,6 +8828,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8679,6 +8969,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8815,6 +9110,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8951,6 +9251,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9087,6 +9392,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9223,6 +9533,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9359,6 +9674,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9495,6 +9815,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9631,6 +9956,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9767,6 +10097,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9903,6 +10238,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10039,6 +10379,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10175,6 +10520,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10311,6 +10661,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10447,6 +10802,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10583,6 +10943,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10719,6 +11084,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10855,6 +11225,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10991,6 +11366,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11127,6 +11507,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11263,6 +11648,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11399,6 +11789,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11535,6 +11930,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11671,6 +12071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11807,6 +12212,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11943,6 +12353,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12079,6 +12494,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12224,6 +12644,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12360,6 +12785,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12496,6 +12926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12632,6 +13067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12768,6 +13208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12904,6 +13349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13040,6 +13490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13176,6 +13631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13312,6 +13772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13448,6 +13913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13584,6 +14054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13720,6 +14195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13856,6 +14336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13992,6 +14477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14128,6 +14618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14264,6 +14759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14400,6 +14900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14536,6 +15041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14672,6 +15182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14808,6 +15323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14944,6 +15464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15080,6 +15605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15216,6 +15746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15352,6 +15887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15488,6 +16028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15624,6 +16169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15760,6 +16310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15896,6 +16451,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16041,6 +16601,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16177,6 +16742,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16313,6 +16883,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16449,6 +17024,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16585,6 +17165,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16721,6 +17306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16857,6 +17447,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16993,6 +17588,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17129,6 +17729,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17265,6 +17870,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17401,6 +18011,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17537,6 +18152,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17673,6 +18293,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17809,6 +18434,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17945,6 +18575,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18081,6 +18716,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18217,6 +18857,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18353,6 +18998,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18489,6 +19139,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18625,6 +19280,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18761,6 +19421,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18897,6 +19562,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19033,6 +19703,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19169,6 +19844,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19305,6 +19985,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19441,6 +20126,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19577,6 +20267,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19713,6 +20408,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19858,6 +20558,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20003,6 +20708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20139,6 +20849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20275,6 +20990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20411,6 +21131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20547,6 +21272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20683,6 +21413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20819,6 +21554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20955,6 +21695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21091,6 +21836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21227,6 +21977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21363,6 +22118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21499,6 +22259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21635,6 +22400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21771,6 +22541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21907,6 +22682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22043,6 +22823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22179,6 +22964,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22315,6 +23105,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22451,6 +23246,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22587,6 +23387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22723,6 +23528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22859,6 +23669,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22995,6 +23810,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23131,6 +23951,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23267,6 +24092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23403,6 +24233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23539,6 +24374,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23675,6 +24515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23820,6 +24665,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23965,6 +24815,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24101,6 +24956,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24237,6 +25097,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24373,6 +25238,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24509,6 +25379,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24645,6 +25520,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24781,6 +25661,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24917,6 +25802,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25053,6 +25943,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25189,6 +26084,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25325,6 +26225,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25461,6 +26366,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25597,6 +26507,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25733,6 +26648,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25869,6 +26789,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26005,6 +26930,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26141,6 +27071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26277,6 +27212,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26413,6 +27353,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26549,6 +27494,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26685,6 +27635,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26821,6 +27776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26957,6 +27917,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27093,6 +28058,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27229,6 +28199,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27365,6 +28340,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27501,6 +28481,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27637,6 +28622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27780,6 +28770,11 @@
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">

--- a/diseases/d118/2026-2029.xlsx
+++ b/diseases/d118/2026-2029.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,11 +894,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -926,22 +906,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1050,11 +1020,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1067,22 +1032,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1191,11 +1146,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1208,22 +1158,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1332,11 +1272,6 @@
       <c r="R6" t="n">
         <v>0.03358077438877618</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1349,22 +1284,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1473,11 +1398,6 @@
       <c r="R7" t="n">
         <v>0.1182514565623162</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1490,22 +1410,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1614,11 +1524,6 @@
       <c r="R8" t="n">
         <v>0.1661131775590399</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1631,22 +1536,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1755,11 +1650,6 @@
       <c r="R9" t="n">
         <v>0.7227710463700993</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1772,22 +1662,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1896,11 +1776,6 @@
       <c r="R10" t="n">
         <v>0.08005301644435721</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1913,22 +1788,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2037,11 +1902,6 @@
       <c r="R11" t="n">
         <v>0.01423577315978787</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2054,22 +1914,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2178,11 +2028,6 @@
       <c r="R12" t="n">
         <v>0.2423077652509323</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2195,22 +2040,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2319,11 +2154,6 @@
       <c r="R13" t="n">
         <v>0.03394067915977812</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2336,22 +2166,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2460,11 +2280,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2477,22 +2292,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2601,11 +2406,6 @@
       <c r="R15" t="n">
         <v>0.02284063495137914</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2618,22 +2418,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2742,11 +2532,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2759,22 +2544,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2883,11 +2658,6 @@
       <c r="R17" t="n">
         <v>0.06260972354050473</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2900,22 +2670,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3024,11 +2784,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3041,22 +2796,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3165,11 +2910,6 @@
       <c r="R19" t="n">
         <v>0.1254972199855829</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3182,22 +2922,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3306,11 +3036,6 @@
       <c r="R20" t="n">
         <v>0.1161075411267424</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3323,22 +3048,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3447,11 +3162,6 @@
       <c r="R21" t="n">
         <v>0.05774110447762056</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3464,22 +3174,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3588,11 +3288,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3605,22 +3300,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3729,11 +3414,6 @@
       <c r="R23" t="n">
         <v>0.2628079452097996</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3746,22 +3426,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3870,11 +3540,6 @@
       <c r="R24" t="n">
         <v>0.0445104504751357</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3887,22 +3552,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4011,11 +3666,6 @@
       <c r="R25" t="n">
         <v>0.3608910110349645</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4028,22 +3678,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4152,11 +3792,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4169,22 +3804,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4293,11 +3918,6 @@
       <c r="R27" t="n">
         <v>0.7579201354866696</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4310,22 +3930,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4434,11 +4044,6 @@
       <c r="R28" t="n">
         <v>0.1879706314685393</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4451,22 +4056,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4575,11 +4170,6 @@
       <c r="R29" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4592,22 +4182,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4725,11 +4305,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4742,22 +4317,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4866,11 +4431,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4883,22 +4443,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5007,11 +4557,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5024,22 +4569,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5148,11 +4683,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5165,22 +4695,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5289,11 +4809,6 @@
       <c r="R34" t="n">
         <v>0.04701308414428665</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5306,22 +4821,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5430,11 +4935,6 @@
       <c r="R35" t="n">
         <v>0.1290015889770722</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5447,22 +4947,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5571,11 +5061,6 @@
       <c r="R36" t="n">
         <v>0.132890542047232</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5588,22 +5073,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5712,11 +5187,6 @@
       <c r="R37" t="n">
         <v>0.8432328874317824</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5729,22 +5199,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5853,11 +5313,6 @@
       <c r="R38" t="n">
         <v>0.02668433881478574</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5870,22 +5325,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5994,11 +5439,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6011,22 +5451,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6135,11 +5565,6 @@
       <c r="R40" t="n">
         <v>0.2516272946836605</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6152,22 +5577,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6276,11 +5691,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6293,22 +5703,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6417,11 +5817,6 @@
       <c r="R42" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6434,22 +5829,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6558,11 +5943,6 @@
       <c r="R43" t="n">
         <v>0.01142031747568957</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6575,22 +5955,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6699,11 +6069,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6716,22 +6081,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6840,11 +6195,6 @@
       <c r="R45" t="n">
         <v>0.03130486177025237</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6857,22 +6207,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6981,11 +6321,6 @@
       <c r="R46" t="n">
         <v>0.05895154094906676</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6998,22 +6333,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7122,11 +6447,6 @@
       <c r="R47" t="n">
         <v>0.1422301826503273</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7139,22 +6459,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7263,11 +6573,6 @@
       <c r="R48" t="n">
         <v>0.1625505575774394</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7280,22 +6585,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7404,11 +6699,6 @@
       <c r="R49" t="n">
         <v>0.05774110447762056</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7421,22 +6711,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7545,11 +6825,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7562,22 +6837,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7686,11 +6951,6 @@
       <c r="R51" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7703,22 +6963,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7827,11 +7077,6 @@
       <c r="R52" t="n">
         <v>0.06231463066518999</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7844,22 +7089,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7968,11 +7203,6 @@
       <c r="R53" t="n">
         <v>0.3007425091958037</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7985,22 +7215,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8109,11 +7329,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8126,22 +7341,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8250,11 +7455,6 @@
       <c r="R55" t="n">
         <v>0.5890122195782118</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8267,22 +7467,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8391,11 +7581,6 @@
       <c r="R56" t="n">
         <v>0.3759412629370787</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8408,22 +7593,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8532,11 +7707,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8549,22 +7719,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8682,11 +7842,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8699,22 +7854,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8823,11 +7968,6 @@
       <c r="R59" t="n">
         <v>0.03104502522097849</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8840,22 +7980,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8964,11 +8094,6 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8981,22 +8106,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9105,11 +8220,6 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9122,22 +8232,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9246,11 +8346,6 @@
       <c r="R62" t="n">
         <v>0.05372923902204188</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9263,22 +8358,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9387,11 +8472,6 @@
       <c r="R63" t="n">
         <v>0.1290015889770722</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9404,22 +8484,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9528,11 +8598,6 @@
       <c r="R64" t="n">
         <v>0.132890542047232</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9545,22 +8610,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9669,11 +8724,6 @@
       <c r="R65" t="n">
         <v>1.276895515253842</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9686,22 +8736,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9810,11 +8850,6 @@
       <c r="R66" t="n">
         <v>0.0400265082221786</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9827,22 +8862,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9951,11 +8976,6 @@
       <c r="R67" t="n">
         <v>0.01423577315978787</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9968,22 +8988,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10092,11 +9102,6 @@
       <c r="R68" t="n">
         <v>0.3355030595782139</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10109,22 +9114,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10233,11 +9228,6 @@
       <c r="R69" t="n">
         <v>0.1357627166391125</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10250,22 +9240,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10374,11 +9354,6 @@
       <c r="R70" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10391,22 +9366,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10515,11 +9480,6 @@
       <c r="R71" t="n">
         <v>0.02284063495137914</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10532,22 +9492,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10656,11 +9606,6 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10673,22 +9618,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10797,11 +9732,6 @@
       <c r="R73" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10814,22 +9744,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10938,11 +9858,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10955,22 +9870,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11079,11 +9984,6 @@
       <c r="R75" t="n">
         <v>0.02509944399711657</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11096,22 +9996,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11220,11 +10110,6 @@
       <c r="R76" t="n">
         <v>0.1509398034647651</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11237,22 +10122,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11361,11 +10236,6 @@
       <c r="R77" t="n">
         <v>0.02887055223881028</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11378,22 +10248,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11502,11 +10362,6 @@
       <c r="R78" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11519,22 +10374,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11643,11 +10488,6 @@
       <c r="R79" t="n">
         <v>0.3942119178146994</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11660,22 +10500,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11784,11 +10614,6 @@
       <c r="R80" t="n">
         <v>0.02670627028508142</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11801,22 +10626,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11925,11 +10740,6 @@
       <c r="R81" t="n">
         <v>0.1563861047818179</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11942,22 +10752,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12066,11 +10866,6 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12083,22 +10878,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12207,11 +10992,6 @@
       <c r="R83" t="n">
         <v>0.710279441256079</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12224,22 +11004,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12348,11 +11118,6 @@
       <c r="R84" t="n">
         <v>0.3759412629370787</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12365,22 +11130,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12489,11 +11244,6 @@
       <c r="R85" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12506,22 +11256,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12639,11 +11379,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12656,22 +11391,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12780,11 +11505,6 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12797,22 +11517,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12921,11 +11631,6 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12938,22 +11643,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13062,11 +11757,6 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13079,22 +11769,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13203,11 +11883,6 @@
       <c r="R90" t="n">
         <v>0.04029692926653142</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13220,22 +11895,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13344,11 +12009,6 @@
       <c r="R91" t="n">
         <v>0.04300052965902407</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13361,22 +12021,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13485,11 +12135,6 @@
       <c r="R92" t="n">
         <v>0.03322263551180799</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13502,22 +12147,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13626,11 +12261,6 @@
       <c r="R93" t="n">
         <v>0.9396023602811291</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13643,22 +12273,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13767,11 +12387,6 @@
       <c r="R94" t="n">
         <v>0.02668433881478574</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13784,22 +12399,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13908,11 +12513,6 @@
       <c r="R95" t="n">
         <v>0.01423577315978787</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13925,22 +12525,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14049,11 +12639,6 @@
       <c r="R96" t="n">
         <v>0.3401628242945781</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14066,22 +12651,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14190,11 +12765,6 @@
       <c r="R97" t="n">
         <v>0.03394067915977812</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14207,22 +12777,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14331,11 +12891,6 @@
       <c r="R98" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14348,22 +12903,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14472,11 +13017,6 @@
       <c r="R99" t="n">
         <v>0.02284063495137914</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14489,22 +13029,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14613,11 +13143,6 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14630,22 +13155,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14754,11 +13269,6 @@
       <c r="R101" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14771,22 +13281,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14895,11 +13395,6 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14912,22 +13407,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15036,11 +13521,6 @@
       <c r="R103" t="n">
         <v>0.1087642573208385</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15053,22 +13533,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15177,11 +13647,6 @@
       <c r="R104" t="n">
         <v>0.1277182952394167</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15194,22 +13659,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15318,11 +13773,6 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15335,22 +13785,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15459,11 +13899,6 @@
       <c r="R106" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15476,22 +13911,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15600,11 +14025,6 @@
       <c r="R107" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15617,22 +14037,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15741,11 +14151,6 @@
       <c r="R108" t="n">
         <v>0.0445104504751357</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15758,22 +14163,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15882,11 +14277,6 @@
       <c r="R109" t="n">
         <v>0.1684158051496501</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15899,22 +14289,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16023,11 +14403,6 @@
       <c r="R110" t="n">
         <v>0.04334154655640577</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16040,22 +14415,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16164,11 +14529,6 @@
       <c r="R111" t="n">
         <v>0.7860714548047459</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16181,22 +14541,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16305,11 +14655,6 @@
       <c r="R112" t="n">
         <v>0.4385981400932585</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16322,22 +14667,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16446,11 +14781,6 @@
       <c r="R113" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16463,22 +14793,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16596,11 +14916,6 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16613,22 +14928,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16737,11 +15042,6 @@
       <c r="R115" t="n">
         <v>0.03104502522097849</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16754,22 +15054,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16878,11 +15168,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16895,22 +15180,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17019,11 +15294,6 @@
       <c r="R117" t="n">
         <v>0.1234639540812862</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17036,22 +15306,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17160,11 +15420,6 @@
       <c r="R118" t="n">
         <v>0.03358077438877618</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17177,22 +15432,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17301,11 +15546,6 @@
       <c r="R119" t="n">
         <v>0.0537506620737801</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17318,22 +15558,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17442,11 +15672,6 @@
       <c r="R120" t="n">
         <v>0.1661131775590399</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17459,22 +15684,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17583,11 +15798,6 @@
       <c r="R121" t="n">
         <v>1.132341305979822</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17600,22 +15810,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17724,11 +15924,6 @@
       <c r="R122" t="n">
         <v>0.05336867762957147</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17741,22 +15936,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17865,11 +16050,6 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17882,22 +16062,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18006,11 +16176,6 @@
       <c r="R124" t="n">
         <v>0.5498522365309617</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18023,22 +16188,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18147,11 +16302,6 @@
       <c r="R125" t="n">
         <v>0.03394067915977812</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18164,22 +16314,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18288,11 +16428,6 @@
       <c r="R126" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18305,22 +16440,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18429,11 +16554,6 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18446,22 +16566,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18570,11 +16680,6 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18587,22 +16692,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -18711,11 +16806,6 @@
       <c r="R129" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18728,22 +16818,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18852,11 +16932,6 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18869,22 +16944,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -18993,11 +17058,6 @@
       <c r="R131" t="n">
         <v>0.05856536932660535</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19010,22 +17070,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19134,11 +17184,6 @@
       <c r="R132" t="n">
         <v>0.2438258363661591</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19151,22 +17196,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19275,11 +17310,6 @@
       <c r="R133" t="n">
         <v>0.08661165671643084</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19292,22 +17322,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -19416,11 +17436,6 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19433,22 +17448,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19557,11 +17562,6 @@
       <c r="R135" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19574,22 +17574,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19698,11 +17688,6 @@
       <c r="R136" t="n">
         <v>0.01780418019005428</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19715,22 +17700,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -19839,11 +17814,6 @@
       <c r="R137" t="n">
         <v>0.1202970036783215</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19856,22 +17826,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19980,11 +17940,6 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19997,22 +17952,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20121,11 +18066,6 @@
       <c r="R139" t="n">
         <v>0.8510360378464605</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20138,22 +18078,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20262,11 +18192,6 @@
       <c r="R140" t="n">
         <v>0.1879706314685393</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20279,22 +18204,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -20403,11 +18318,6 @@
       <c r="R141" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20420,22 +18330,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -20553,11 +18453,6 @@
       <c r="R142" t="n">
         <v>0.1605886125373089</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20570,22 +18465,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -20703,11 +18588,6 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20720,22 +18600,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -20844,11 +18714,6 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20861,22 +18726,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -20985,11 +18840,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21002,22 +18852,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21126,11 +18966,6 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21143,22 +18978,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -21267,11 +19092,6 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21284,22 +19104,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21408,11 +19218,6 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21425,22 +19230,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21549,11 +19344,6 @@
       <c r="R149" t="n">
         <v>0.2657810840944639</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21566,22 +19356,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21690,11 +19470,6 @@
       <c r="R150" t="n">
         <v>1.662373406651228</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21707,22 +19482,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -21831,11 +19596,6 @@
       <c r="R151" t="n">
         <v>0.1601060328887144</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21848,22 +19608,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -21972,11 +19722,6 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21989,22 +19734,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -22113,11 +19848,6 @@
       <c r="R153" t="n">
         <v>0.2329882358182041</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22130,22 +19860,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -22254,11 +19974,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22271,22 +19986,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -22395,11 +20100,6 @@
       <c r="R155" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22412,22 +20112,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -22536,11 +20226,6 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22553,22 +20238,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -22677,11 +20352,6 @@
       <c r="R157" t="n">
         <v>0.02390727039218443</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22694,22 +20364,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -22818,11 +20478,6 @@
       <c r="R158" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22835,22 +20490,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22959,11 +20604,6 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22976,22 +20616,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -23100,11 +20730,6 @@
       <c r="R160" t="n">
         <v>0.06693185065897754</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23117,22 +20742,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -23241,11 +20856,6 @@
       <c r="R161" t="n">
         <v>0.145134426408428</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23258,22 +20868,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -23382,11 +20982,6 @@
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23399,22 +20994,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -23523,11 +21108,6 @@
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23540,22 +21120,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -23664,11 +21234,6 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23681,22 +21246,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23805,11 +21360,6 @@
       <c r="R165" t="n">
         <v>0.00890209009502714</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23822,22 +21372,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -23946,11 +21486,6 @@
       <c r="R166" t="n">
         <v>0.07217820220699288</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23963,22 +21498,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24087,11 +21612,6 @@
       <c r="R167" t="n">
         <v>0.04334154655640577</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24104,22 +21624,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -24228,11 +21738,6 @@
       <c r="R168" t="n">
         <v>0.3421468040196965</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24245,22 +21750,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24369,11 +21864,6 @@
       <c r="R169" t="n">
         <v>0.1879706314685393</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24386,22 +21876,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -24510,11 +21990,6 @@
       <c r="R170" t="n">
         <v>0.04065810840590128</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24527,22 +22002,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -24660,11 +22125,6 @@
       <c r="R171" t="n">
         <v>0.003734618896216486</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24677,22 +22137,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -24810,11 +22260,6 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24827,22 +22272,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -24951,11 +22386,6 @@
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24968,22 +22398,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -25092,11 +22512,6 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25109,22 +22524,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -25233,11 +22638,6 @@
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25250,22 +22650,12 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -25374,11 +22764,6 @@
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25391,22 +22776,12 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -25515,11 +22890,6 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25532,22 +22902,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -25656,11 +23016,6 @@
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25673,22 +23028,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -25797,11 +23142,6 @@
       <c r="R179" t="n">
         <v>0.1927389456986931</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25814,22 +23154,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -25938,11 +23268,6 @@
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25955,22 +23280,12 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -26079,11 +23394,6 @@
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26096,22 +23406,12 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -26220,11 +23520,6 @@
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26237,22 +23532,12 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -26361,11 +23646,6 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26378,22 +23658,12 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -26502,11 +23772,6 @@
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26519,22 +23784,12 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -26643,11 +23898,6 @@
       <c r="R185" t="n">
         <v>0</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26660,22 +23910,12 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -26784,11 +24024,6 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26801,22 +24036,12 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -26925,11 +24150,6 @@
       <c r="R187" t="n">
         <v>0</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26942,22 +24162,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -27066,11 +24276,6 @@
       <c r="R188" t="n">
         <v>0</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27083,22 +24288,12 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -27207,11 +24402,6 @@
       <c r="R189" t="n">
         <v>0</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27224,22 +24414,12 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -27348,11 +24528,6 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27365,22 +24540,12 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -27489,11 +24654,6 @@
       <c r="R191" t="n">
         <v>0</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27506,22 +24666,12 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -27630,11 +24780,6 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27647,22 +24792,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -27771,11 +24906,6 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27788,22 +24918,12 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -27912,11 +25032,6 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27929,22 +25044,12 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -28053,11 +25158,6 @@
       <c r="R195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28070,22 +25170,12 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -28194,11 +25284,6 @@
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28211,22 +25296,12 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -28335,11 +25410,6 @@
       <c r="R197" t="n">
         <v>0</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28352,22 +25422,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -28476,11 +25536,6 @@
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28493,22 +25548,12 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -28617,11 +25662,6 @@
       <c r="R199" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28634,22 +25674,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -28767,11 +25797,6 @@
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28784,22 +25809,12 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>

--- a/diseases/d118/2026-2029.xlsx
+++ b/diseases/d118/2026-2029.xlsx
@@ -4170,6 +4170,11 @@
       <c r="R29" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4182,12 +4187,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -7707,6 +7722,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7719,12 +7739,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -11244,6 +11274,11 @@
       <c r="R85" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11256,12 +11291,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14781,6 +14826,11 @@
       <c r="R113" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14793,12 +14843,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18318,6 +18378,11 @@
       <c r="R141" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18330,12 +18395,22 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -21990,6 +22065,11 @@
       <c r="R170" t="n">
         <v>0.04065810840590128</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22002,12 +22082,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -25662,6 +25752,11 @@
       <c r="R199" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25674,12 +25769,22 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -25797,6 +25902,11 @@
       <c r="R200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25809,13 +25919,23 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
       </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV200" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25852,6 +25972,156 @@
         </is>
       </c>
       <c r="BC200" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>spotted-fever-rickettsiosis</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Spotted fever rickettsiosis</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Spotted fever rickettsiosis</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>斑点热立克次体病</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>2</v>
+      </c>
+      <c r="O201" t="n">
+        <v>2</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -25890,7 +26160,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -25973,7 +26243,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -25983,7 +26253,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -26035,7 +26305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3491</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="16">
